--- a/dados.xlsx
+++ b/dados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/DASHBOARD POSICIONAMENTO COMERCIAL/Teste 3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/DASHBOARD POSICIONAMENTO COMERCIAL/Teste 17/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="8_{9FEF56CC-3B5E-48FD-96FB-5F7F1FD2C0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454497A0-57CA-4C48-BB25-02DC88F2EAF0}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{9FEF56CC-3B5E-48FD-96FB-5F7F1FD2C0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16B8EDF5-7660-43EE-8AD6-53258B4C0DB0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{6C7AE323-4709-4BDF-A571-C7C584D36725}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6C7AE323-4709-4BDF-A571-C7C584D36725}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas Mensal 2026" sheetId="1" r:id="rId1"/>
@@ -9175,8 +9175,12 @@
       <c r="C69" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+      <c r="D69" s="2">
+        <v>1920</v>
+      </c>
+      <c r="E69" s="2">
+        <v>3359</v>
+      </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
@@ -9188,8 +9192,12 @@
       <c r="C70" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
+      <c r="D70" s="3">
+        <v>1920</v>
+      </c>
+      <c r="E70" s="3">
+        <v>2986</v>
+      </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
@@ -9201,8 +9209,12 @@
       <c r="C71" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="D71" s="2">
+        <v>396.5</v>
+      </c>
+      <c r="E71" s="2">
+        <v>1120</v>
+      </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
@@ -9214,8 +9226,12 @@
       <c r="C72" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
+      <c r="D72" s="3">
+        <v>1476</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3246</v>
+      </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
@@ -9227,8 +9243,12 @@
       <c r="C73" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
+      <c r="D73" s="2">
+        <v>1118</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2164</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
@@ -9240,8 +9260,12 @@
       <c r="C74" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
+      <c r="D74" s="3">
+        <v>846.5</v>
+      </c>
+      <c r="E74" s="3">
+        <v>1710</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
@@ -9253,8 +9277,12 @@
       <c r="C75" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+      <c r="D75" s="2">
+        <v>1395.5</v>
+      </c>
+      <c r="E75" s="2">
+        <v>1610</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
@@ -9266,8 +9294,12 @@
       <c r="C76" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
+      <c r="D76" s="3">
+        <v>269</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1120</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
@@ -9279,8 +9311,12 @@
       <c r="C77" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
+      <c r="D77" s="2">
+        <v>542</v>
+      </c>
+      <c r="E77" s="2">
+        <v>1405</v>
+      </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
@@ -9292,8 +9328,12 @@
       <c r="C78" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
+      <c r="D78" s="3">
+        <v>456.5</v>
+      </c>
+      <c r="E78" s="3">
+        <v>1000</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
